--- a/ig/feature-good-practices-interop/StructureDefinition-as-mailbox-mss-metadata.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-mailbox-mss-metadata.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
